--- a/public/excel/4/Surat_Jalan_By_RIFARA.xlsx
+++ b/public/excel/4/Surat_Jalan_By_RIFARA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ExcelTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FC42612-3CB5-47A1-BC2A-AD8534E1162B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C0D610C-C481-4BF0-B4B1-45D56ECEDA1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{3B367BED-561D-4398-82D9-751D32DFA537}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{3B367BED-561D-4398-82D9-751D32DFA537}"/>
   </bookViews>
   <sheets>
     <sheet name="Database" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="129">
   <si>
     <t>No.</t>
   </si>
@@ -327,9 +327,6 @@
   </si>
   <si>
     <t>TLS-75</t>
-  </si>
-  <si>
-    <t>Lusin</t>
   </si>
   <si>
     <t>Box</t>
@@ -449,6 +446,15 @@
   </si>
   <si>
     <t>Nama Penerima</t>
+  </si>
+  <si>
+    <t>Pipa Air 1 Inch</t>
+  </si>
+  <si>
+    <t>Meter</t>
+  </si>
+  <si>
+    <t>PAI-85</t>
   </si>
 </sst>
 </file>
@@ -460,7 +466,7 @@
     <numFmt numFmtId="165" formatCode="@\ * \:"/>
     <numFmt numFmtId="166" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -516,6 +522,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="1"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -531,7 +546,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -563,20 +578,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -622,6 +628,27 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -637,49 +664,36 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="16">
     <dxf>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="164" formatCode="0.00000"/>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -701,13 +715,6 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.00000"/>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -795,22 +802,77 @@
     </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>3451</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>3451</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>4257</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="4" name="Straight Connector 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0B99FD7C-9D27-3A91-EEA0-1BF0DC9392D2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="741424" y="5862595"/>
+          <a:ext cx="0" cy="755959"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3F651FFC-8AF7-4FAE-9761-99788937261D}" name="Data_Tujuan" displayName="Data_Tujuan" ref="B3:J15" totalsRowShown="0" headerRowDxfId="17">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3F651FFC-8AF7-4FAE-9761-99788937261D}" name="Data_Tujuan" displayName="Data_Tujuan" ref="B3:J15" totalsRowShown="0" headerRowDxfId="15">
   <autoFilter ref="B3:J15" xr:uid="{3F651FFC-8AF7-4FAE-9761-99788937261D}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{C0B27E33-E86D-4B26-9CF0-6D137263375B}" name="No." dataDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{9EA6417A-F0CB-4EFD-9ABB-46E191043AE8}" name="No Surat Jalan" dataDxfId="15"/>
-    <tableColumn id="3" xr3:uid="{9C7C035E-00EF-4E98-AF8F-E69224FBAE20}" name="Tanggal" dataDxfId="14"/>
-    <tableColumn id="4" xr3:uid="{2005B3B6-DB14-4F54-9B40-2092113F2CE4}" name="No. PO/Ref" dataDxfId="13"/>
-    <tableColumn id="5" xr3:uid="{275FD74A-F40E-499A-8ABB-3DF87C97B893}" name="Nama Supir" dataDxfId="12"/>
-    <tableColumn id="6" xr3:uid="{FBBCC378-C45C-4415-BF62-AEBE1DEE364B}" name="No. Polisi" dataDxfId="11">
+    <tableColumn id="1" xr3:uid="{C0B27E33-E86D-4B26-9CF0-6D137263375B}" name="No." dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{9EA6417A-F0CB-4EFD-9ABB-46E191043AE8}" name="No Surat Jalan" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{9C7C035E-00EF-4E98-AF8F-E69224FBAE20}" name="Tanggal" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{2005B3B6-DB14-4F54-9B40-2092113F2CE4}" name="No. PO/Ref" dataDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{275FD74A-F40E-499A-8ABB-3DF87C97B893}" name="Nama Supir" dataDxfId="10"/>
+    <tableColumn id="6" xr3:uid="{FBBCC378-C45C-4415-BF62-AEBE1DEE364B}" name="No. Polisi" dataDxfId="1">
       <calculatedColumnFormula>"B "&amp;RIGHT(RAND(),4)&amp;" AB"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{718661DA-8815-4CD8-B7F7-772D60E331D9}" name="Nama Perusahaan" dataDxfId="10"/>
+    <tableColumn id="7" xr3:uid="{718661DA-8815-4CD8-B7F7-772D60E331D9}" name="Nama Perusahaan" dataDxfId="0"/>
     <tableColumn id="8" xr3:uid="{657F788D-0DB3-476F-8B59-B86C210B7119}" name="Untuk Perhatian" dataDxfId="9"/>
     <tableColumn id="9" xr3:uid="{BEDD1C98-4155-4FE4-939B-456B673D9446}" name="Alamat Perusahaan" dataDxfId="8"/>
   </tableColumns>
@@ -819,15 +881,13 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{F548EB79-0920-4612-8EE5-D5EAEA6F62C6}" name="Data_Barang" displayName="Data_Barang" ref="B17:G24" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
-  <autoFilter ref="B17:G24" xr:uid="{F548EB79-0920-4612-8EE5-D5EAEA6F62C6}"/>
-  <tableColumns count="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{F548EB79-0920-4612-8EE5-D5EAEA6F62C6}" name="Data_Barang" displayName="Data_Barang" ref="B17:E25" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
+  <autoFilter ref="B17:E25" xr:uid="{F548EB79-0920-4612-8EE5-D5EAEA6F62C6}"/>
+  <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{5BBDD02A-8443-458A-852D-2BF9243755B0}" name="No." dataDxfId="5"/>
     <tableColumn id="2" xr3:uid="{18917E34-C7FD-4665-80C9-74712D79B11B}" name="Kode Barang" dataDxfId="4"/>
     <tableColumn id="3" xr3:uid="{0AA95692-F669-44DB-91EB-937FE76F56CF}" name="Nama / Deskripsi Barang" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{8D80A2C7-2891-4396-B2DB-3FB962FD1F84}" name="QTY" dataDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{21D48427-9CED-4994-A509-1EA1F2489D97}" name="Satuan" dataDxfId="1"/>
-    <tableColumn id="7" xr3:uid="{63ACAFB4-38DD-46BC-8A20-FCC667FA9730}" name="Keterangan" dataDxfId="0"/>
+    <tableColumn id="6" xr3:uid="{21D48427-9CED-4994-A509-1EA1F2489D97}" name="Satuan" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1150,7 +1210,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7D5B147-1328-4AC2-BF98-014AB24F362D}">
-  <dimension ref="B3:J24"/>
+  <dimension ref="B3:J25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="5.77734375" customWidth="1"/>
@@ -1190,7 +1250,7 @@
         <v>7</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
@@ -1211,7 +1271,7 @@
       </c>
       <c r="G4" s="12" t="str">
         <f ca="1">"B "&amp;RIGHT(RAND(),4)&amp;" AB"</f>
-        <v>B 6851 AB</v>
+        <v>B 0127 AB</v>
       </c>
       <c r="H4" s="10" t="s">
         <v>44</v>
@@ -1220,7 +1280,7 @@
         <v>55</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.3">
@@ -1241,7 +1301,7 @@
       </c>
       <c r="G5" s="12" t="str">
         <f t="shared" ref="G5:G15" ca="1" si="0">"B "&amp;RIGHT(RAND(),4)&amp;" AB"</f>
-        <v>B 8604 AB</v>
+        <v>B 1051 AB</v>
       </c>
       <c r="H5" s="10" t="s">
         <v>67</v>
@@ -1250,7 +1310,7 @@
         <v>56</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.3">
@@ -1271,7 +1331,7 @@
       </c>
       <c r="G6" s="12" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>B 5169 AB</v>
+        <v>B 6244 AB</v>
       </c>
       <c r="H6" s="10" t="s">
         <v>45</v>
@@ -1280,7 +1340,7 @@
         <v>57</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.3">
@@ -1301,7 +1361,7 @@
       </c>
       <c r="G7" s="12" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>B 3997 AB</v>
+        <v>B 2998 AB</v>
       </c>
       <c r="H7" s="10" t="s">
         <v>46</v>
@@ -1310,7 +1370,7 @@
         <v>58</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.3">
@@ -1331,7 +1391,7 @@
       </c>
       <c r="G8" s="12" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>B 8635 AB</v>
+        <v>B 8509 AB</v>
       </c>
       <c r="H8" s="10" t="s">
         <v>47</v>
@@ -1340,7 +1400,7 @@
         <v>59</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.3">
@@ -1361,7 +1421,7 @@
       </c>
       <c r="G9" s="12" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>B 4142 AB</v>
+        <v>B 9051 AB</v>
       </c>
       <c r="H9" s="10" t="s">
         <v>48</v>
@@ -1370,7 +1430,7 @@
         <v>60</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.3">
@@ -1391,7 +1451,7 @@
       </c>
       <c r="G10" s="12" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>B 8522 AB</v>
+        <v>B 6694 AB</v>
       </c>
       <c r="H10" s="10" t="s">
         <v>49</v>
@@ -1400,7 +1460,7 @@
         <v>61</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.3">
@@ -1421,7 +1481,7 @@
       </c>
       <c r="G11" s="12" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>B 1011 AB</v>
+        <v>B 7472 AB</v>
       </c>
       <c r="H11" s="10" t="s">
         <v>50</v>
@@ -1430,7 +1490,7 @@
         <v>62</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.3">
@@ -1451,7 +1511,7 @@
       </c>
       <c r="G12" s="12" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>B 5758 AB</v>
+        <v>B 1936 AB</v>
       </c>
       <c r="H12" s="10" t="s">
         <v>51</v>
@@ -1460,7 +1520,7 @@
         <v>63</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.3">
@@ -1481,7 +1541,7 @@
       </c>
       <c r="G13" s="12" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>B 9749 AB</v>
+        <v>B 4703 AB</v>
       </c>
       <c r="H13" s="10" t="s">
         <v>52</v>
@@ -1490,7 +1550,7 @@
         <v>64</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.3">
@@ -1511,7 +1571,7 @@
       </c>
       <c r="G14" s="12" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>B 2614 AB</v>
+        <v>B 1602 AB</v>
       </c>
       <c r="H14" s="10" t="s">
         <v>53</v>
@@ -1520,7 +1580,7 @@
         <v>65</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.3">
@@ -1541,7 +1601,7 @@
       </c>
       <c r="G15" s="12" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>B 9912 AB</v>
+        <v>B 4092 AB</v>
       </c>
       <c r="H15" s="10" t="s">
         <v>54</v>
@@ -1550,10 +1610,10 @@
         <v>66</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B17" s="2" t="s">
         <v>0</v>
       </c>
@@ -1564,16 +1624,12 @@
         <v>69</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F17" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="G17" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="G17" s="35"/>
+      <c r="H17" s="35"/>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B18" s="1">
         <v>1</v>
       </c>
@@ -1583,17 +1639,13 @@
       <c r="D18" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="E18" s="2">
-        <v>100</v>
-      </c>
-      <c r="F18" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="G18" s="10" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E18" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="G18" s="36"/>
+      <c r="H18" s="36"/>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B19" s="1">
         <v>2</v>
       </c>
@@ -1603,17 +1655,13 @@
       <c r="D19" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="E19" s="2">
-        <v>10</v>
-      </c>
-      <c r="F19" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="G19" s="10" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E19" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="G19" s="36"/>
+      <c r="H19" s="36"/>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B20" s="1">
         <v>3</v>
       </c>
@@ -1623,17 +1671,13 @@
       <c r="D20" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="E20" s="2">
-        <v>5</v>
-      </c>
-      <c r="F20" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="G20" s="10" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E20" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="G20" s="36"/>
+      <c r="H20" s="36"/>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B21" s="1">
         <v>4</v>
       </c>
@@ -1643,17 +1687,13 @@
       <c r="D21" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="E21" s="2">
-        <v>4</v>
-      </c>
-      <c r="F21" s="10" t="s">
+      <c r="E21" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="G21" s="10" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="G21" s="36"/>
+      <c r="H21" s="36"/>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B22" s="1">
         <v>5</v>
       </c>
@@ -1663,17 +1703,13 @@
       <c r="D22" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="E22" s="2">
-        <v>10</v>
-      </c>
-      <c r="F22" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="G22" s="10" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E22" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="G22" s="36"/>
+      <c r="H22" s="36"/>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B23" s="1">
         <v>6</v>
       </c>
@@ -1683,17 +1719,13 @@
       <c r="D23" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="E23" s="2">
-        <v>12</v>
-      </c>
-      <c r="F23" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="G23" s="10" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E23" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="G23" s="36"/>
+      <c r="H23" s="36"/>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B24" s="1">
         <v>7</v>
       </c>
@@ -1703,14 +1735,24 @@
       <c r="D24" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="E24" s="2">
-        <v>12</v>
-      </c>
-      <c r="F24" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="G24" s="10" t="s">
-        <v>92</v>
+      <c r="E24" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="G24" s="36"/>
+      <c r="H24" s="36"/>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B25" s="1">
+        <v>8</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -1726,53 +1768,53 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C23DB7E-5F85-420D-BA72-50B60D6263AC}">
-  <dimension ref="A2:I47"/>
+  <dimension ref="A2:L47"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.77734375" customWidth="1"/>
     <col min="2" max="2" width="4.77734375" customWidth="1"/>
     <col min="3" max="4" width="25.77734375" customWidth="1"/>
-    <col min="5" max="5" width="4.77734375" customWidth="1"/>
+    <col min="5" max="5" width="6.77734375" customWidth="1"/>
     <col min="6" max="6" width="16.33203125" customWidth="1"/>
     <col min="7" max="7" width="25.77734375" customWidth="1"/>
     <col min="8" max="8" width="4.77734375" customWidth="1"/>
     <col min="9" max="9" width="10.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B2" s="28" t="s">
+    <row r="2" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B2" s="22" t="s">
+        <v>92</v>
+      </c>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+    </row>
+    <row r="3" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-    </row>
-    <row r="3" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="29" t="s">
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
+      <c r="H3" s="23"/>
+    </row>
+    <row r="4" spans="1:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
-    </row>
-    <row r="4" spans="1:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="30" t="s">
-        <v>95</v>
-      </c>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="30"/>
-    </row>
-    <row r="5" spans="1:9" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
+    </row>
+    <row r="5" spans="1:12" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -1783,35 +1825,36 @@
       <c r="H5" s="4"/>
       <c r="I5" s="3"/>
     </row>
-    <row r="6" spans="1:9" s="31" customFormat="1" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="33" t="s">
-        <v>96</v>
-      </c>
-      <c r="C6" s="33"/>
-      <c r="D6" s="33"/>
-      <c r="E6" s="33"/>
-      <c r="F6" s="33"/>
-      <c r="G6" s="33"/>
-      <c r="H6" s="33"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" s="20" customFormat="1" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="C6" s="25"/>
+      <c r="D6" s="25"/>
+      <c r="E6" s="25"/>
+      <c r="F6" s="25"/>
+      <c r="G6" s="25"/>
+      <c r="H6" s="25"/>
+    </row>
+    <row r="7" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B8" s="5"/>
       <c r="C8" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>8</v>
       </c>
       <c r="E8" s="8"/>
       <c r="F8" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G8" s="9" t="str">
         <f>_xlfn.XLOOKUP($D$8,Data_Tujuan[No Surat Jalan],Data_Tujuan[Nama Perusahaan])</f>
         <v>PT. BeSmart Global</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B9" s="5"/>
       <c r="C9" s="8" t="s">
         <v>3</v>
@@ -1825,7 +1868,7 @@
         <v>Jl. Jend. Sudirman No. 45</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B10" s="5"/>
       <c r="C10" s="8" t="s">
         <v>4</v>
@@ -1839,7 +1882,7 @@
         <v>Jakarta Barat</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B11" s="5"/>
       <c r="C11" s="8" t="s">
         <v>5</v>
@@ -1849,38 +1892,38 @@
         <v>Rizky</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B12" s="5"/>
       <c r="C12" s="8" t="s">
         <v>6</v>
       </c>
       <c r="D12" s="7" t="str">
         <f ca="1">_xlfn.XLOOKUP($D$8,Data_Tujuan[No Surat Jalan],Data_Tujuan[No. Polisi])</f>
-        <v>B 6851 AB</v>
+        <v>B 0127 AB</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G12" t="str">
         <f>_xlfn.XLOOKUP($D$8,Data_Tujuan[No Surat Jalan],Data_Tujuan[Untuk Perhatian])</f>
         <v>Bapak Jamal</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="32" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="16" spans="1:9" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="21" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="16" spans="1:12" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="17" t="s">
         <v>0</v>
       </c>
       <c r="C16" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="D16" s="18" t="s">
         <v>114</v>
-      </c>
-      <c r="D16" s="18" t="s">
-        <v>115</v>
       </c>
       <c r="E16" s="17" t="s">
         <v>70</v>
@@ -1888,206 +1931,220 @@
       <c r="F16" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="G16" s="19" t="s">
+      <c r="G16" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="H16" s="19"/>
-    </row>
-    <row r="17" spans="2:8" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H16" s="26"/>
+      <c r="L16" s="31"/>
+    </row>
+    <row r="17" spans="1:8" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="13">
         <v>1</v>
       </c>
-      <c r="C17" s="16" t="str" cm="1">
-        <f t="array" ref="C17:C23">_xlfn.TOCOL(Data_Barang[Kode Barang],3)</f>
-        <v>STR-50</v>
-      </c>
-      <c r="D17" s="16" t="str" cm="1">
-        <f t="array" ref="D17:D23">_xlfn.TOCOL(Database!D18:D24)</f>
+      <c r="C17" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="D17" s="32" t="str">
+        <f>IFERROR(VLOOKUP(C17, Data_Barang[[Kode Barang]:[Satuan]], 2, FALSE)," ")</f>
         <v>Semen Tiga Roda 50kg</v>
       </c>
-      <c r="E17" s="15" cm="1">
-        <f t="array" ref="E17:E23">_xlfn.TOCOL(Data_Barang[QTY])</f>
+      <c r="E17" s="15">
         <v>100</v>
       </c>
-      <c r="F17" s="15" t="str" cm="1">
-        <f t="array" ref="F17:F23">_xlfn.TOCOL(Data_Barang[Satuan])</f>
+      <c r="F17" s="15" t="str">
+        <f>IFERROR(VLOOKUP(C17,Data_Barang[[Kode Barang]:[Satuan]],3,FALSE)," ")</f>
         <v>Sak</v>
       </c>
-      <c r="G17" s="22" t="s">
-        <v>92</v>
-      </c>
-      <c r="H17" s="22"/>
-    </row>
-    <row r="18" spans="2:8" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G17" s="29" t="s">
+        <v>91</v>
+      </c>
+      <c r="H17" s="29"/>
+    </row>
+    <row r="18" spans="1:8" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B18" s="13">
         <v>2</v>
       </c>
-      <c r="C18" s="16" t="str">
-        <v>CTDP-25</v>
-      </c>
-      <c r="D18" s="16" t="str">
+      <c r="C18" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="D18" s="32" t="str">
+        <f>IFERROR(VLOOKUP(C18, Data_Barang[[Kode Barang]:[Satuan]], 2, FALSE)," ")</f>
         <v>Cat Tembok Dulux Putih 25kg</v>
       </c>
       <c r="E18" s="15">
         <v>10</v>
       </c>
-      <c r="F18" s="15" t="str">
+      <c r="F18" s="19" t="str">
+        <f>IFERROR(VLOOKUP(C18,Data_Barang[[Kode Barang]:[Satuan]],3,FALSE)," ")</f>
         <v>Pail</v>
       </c>
-      <c r="G18" s="22" t="s">
-        <v>92</v>
-      </c>
-      <c r="H18" s="22"/>
-    </row>
-    <row r="19" spans="2:8" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G18" s="29" t="s">
+        <v>91</v>
+      </c>
+      <c r="H18" s="29"/>
+    </row>
+    <row r="19" spans="1:8" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B19" s="13">
         <v>3</v>
       </c>
-      <c r="C19" s="16" t="str">
-        <v>PP-35</v>
-      </c>
-      <c r="D19" s="16" t="str">
+      <c r="C19" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="D19" s="32" t="str">
+        <f>IFERROR(VLOOKUP(C19, Data_Barang[[Kode Barang]:[Satuan]], 2, FALSE)," ")</f>
         <v>Paku Payung</v>
       </c>
       <c r="E19" s="15">
         <v>5</v>
       </c>
-      <c r="F19" s="15" t="str">
+      <c r="F19" s="19" t="str">
+        <f>IFERROR(VLOOKUP(C19,Data_Barang[[Kode Barang]:[Satuan]],3,FALSE)," ")</f>
         <v>Box</v>
       </c>
-      <c r="G19" s="22" t="s">
-        <v>92</v>
-      </c>
-      <c r="H19" s="22"/>
-    </row>
-    <row r="20" spans="2:8" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G19" s="29" t="s">
+        <v>91</v>
+      </c>
+      <c r="H19" s="29"/>
+    </row>
+    <row r="20" spans="1:8" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B20" s="13">
         <v>4</v>
       </c>
-      <c r="C20" s="16" t="str">
-        <v>KCI-45</v>
-      </c>
-      <c r="D20" s="16" t="str">
+      <c r="C20" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="D20" s="32" t="str">
+        <f>IFERROR(VLOOKUP(C20, Data_Barang[[Kode Barang]:[Satuan]], 2, FALSE)," ")</f>
         <v>Kuas Cat 4 Inch</v>
       </c>
       <c r="E20" s="15">
         <v>4</v>
       </c>
-      <c r="F20" s="15" t="str">
-        <v>Lusin</v>
-      </c>
-      <c r="G20" s="22" t="s">
-        <v>92</v>
-      </c>
-      <c r="H20" s="22"/>
-    </row>
-    <row r="21" spans="2:8" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F20" s="19" t="str">
+        <f>IFERROR(VLOOKUP(C20,Data_Barang[[Kode Barang]:[Satuan]],3,FALSE)," ")</f>
+        <v>Box</v>
+      </c>
+      <c r="G20" s="29" t="s">
+        <v>91</v>
+      </c>
+      <c r="H20" s="29"/>
+    </row>
+    <row r="21" spans="1:8" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B21" s="13">
         <v>5</v>
       </c>
-      <c r="C21" s="16" t="str">
-        <v>MAS-55</v>
-      </c>
-      <c r="D21" s="16" t="str">
+      <c r="C21" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="D21" s="32" t="str">
+        <f>IFERROR(VLOOKUP(C21, Data_Barang[[Kode Barang]:[Satuan]], 2, FALSE)," ")</f>
         <v>Mesin Air Shimizu</v>
       </c>
       <c r="E21" s="15">
         <v>10</v>
       </c>
-      <c r="F21" s="15" t="str">
+      <c r="F21" s="19" t="str">
+        <f>IFERROR(VLOOKUP(C21,Data_Barang[[Kode Barang]:[Satuan]],3,FALSE)," ")</f>
         <v>Pieces</v>
       </c>
-      <c r="G21" s="22" t="s">
-        <v>92</v>
-      </c>
-      <c r="H21" s="22"/>
-    </row>
-    <row r="22" spans="2:8" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G21" s="29" t="s">
+        <v>91</v>
+      </c>
+      <c r="H21" s="29"/>
+    </row>
+    <row r="22" spans="1:8" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B22" s="13">
         <v>6</v>
       </c>
-      <c r="C22" s="16" t="str">
-        <v>MAS-65</v>
-      </c>
-      <c r="D22" s="16" t="str">
-        <v>Mesin Air Sanyo</v>
+      <c r="C22" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="D22" s="32" t="str">
+        <f>IFERROR(VLOOKUP(C22, Data_Barang[[Kode Barang]:[Satuan]], 2, FALSE)," ")</f>
+        <v>Tabung 12 Liter Shimizu</v>
       </c>
       <c r="E22" s="15">
         <v>12</v>
       </c>
-      <c r="F22" s="15" t="str">
+      <c r="F22" s="19" t="str">
+        <f>IFERROR(VLOOKUP(C22,Data_Barang[[Kode Barang]:[Satuan]],3,FALSE)," ")</f>
         <v>Pieces</v>
       </c>
-      <c r="G22" s="22" t="s">
-        <v>92</v>
-      </c>
-      <c r="H22" s="22"/>
-    </row>
-    <row r="23" spans="2:8" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G22" s="29" t="s">
+        <v>91</v>
+      </c>
+      <c r="H22" s="29"/>
+    </row>
+    <row r="23" spans="1:8" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B23" s="13">
         <v>7</v>
       </c>
-      <c r="C23" s="16" t="str">
-        <v>TLS-75</v>
-      </c>
-      <c r="D23" s="16" t="str">
-        <v>Tabung 12 Liter Shimizu</v>
+      <c r="C23" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="D23" s="32" t="str">
+        <f>IFERROR(VLOOKUP(C23, Data_Barang[[Kode Barang]:[Satuan]], 2, FALSE)," ")</f>
+        <v>Pipa Air 1 Inch</v>
       </c>
       <c r="E23" s="15">
         <v>12</v>
       </c>
-      <c r="F23" s="15" t="str">
-        <v>Pieces</v>
-      </c>
-      <c r="G23" s="22" t="s">
-        <v>92</v>
-      </c>
-      <c r="H23" s="22"/>
-    </row>
-    <row r="26" spans="2:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="24" t="s">
+      <c r="F23" s="19" t="str">
+        <f>IFERROR(VLOOKUP(C23,Data_Barang[[Kode Barang]:[Satuan]],3,FALSE)," ")</f>
+        <v>Meter</v>
+      </c>
+      <c r="G23" s="29" t="s">
+        <v>91</v>
+      </c>
+      <c r="H23" s="29"/>
+    </row>
+    <row r="26" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="3"/>
+      <c r="B26" s="34" t="s">
+        <v>115</v>
+      </c>
+      <c r="C26" s="34"/>
+      <c r="D26" s="34"/>
+      <c r="E26" s="34"/>
+      <c r="F26" s="34"/>
+      <c r="G26" s="34"/>
+      <c r="H26" s="34"/>
+    </row>
+    <row r="27" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="3"/>
+      <c r="B27" s="33" t="s">
         <v>116</v>
       </c>
-      <c r="C26" s="25"/>
-      <c r="D26" s="25"/>
-      <c r="E26" s="25"/>
-      <c r="F26" s="25"/>
-      <c r="G26" s="25"/>
-      <c r="H26" s="25"/>
-    </row>
-    <row r="27" spans="2:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="26" t="s">
+      <c r="C27" s="33"/>
+      <c r="D27" s="33"/>
+      <c r="E27" s="33"/>
+      <c r="F27" s="33"/>
+      <c r="G27" s="33"/>
+      <c r="H27" s="33"/>
+    </row>
+    <row r="28" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="3"/>
+      <c r="B28" s="33" t="s">
         <v>117</v>
       </c>
-      <c r="C27" s="27"/>
-      <c r="D27" s="27"/>
-      <c r="E27" s="27"/>
-      <c r="F27" s="27"/>
-      <c r="G27" s="27"/>
-      <c r="H27" s="27"/>
-    </row>
-    <row r="28" spans="2:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="26" t="s">
-        <v>118</v>
-      </c>
-      <c r="C28" s="27"/>
-      <c r="D28" s="27"/>
-      <c r="E28" s="27"/>
-      <c r="F28" s="27"/>
-      <c r="G28" s="27"/>
-      <c r="H28" s="27"/>
+      <c r="C28" s="33"/>
+      <c r="D28" s="33"/>
+      <c r="E28" s="33"/>
+      <c r="F28" s="33"/>
+      <c r="G28" s="33"/>
+      <c r="H28" s="33"/>
     </row>
     <row r="37" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C37" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D37" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="D37" s="23" t="s">
+      <c r="E37" s="30"/>
+      <c r="F37" s="30"/>
+      <c r="G37" s="2" t="s">
         <v>120</v>
-      </c>
-      <c r="E37" s="23"/>
-      <c r="F37" s="23"/>
-      <c r="G37" s="2" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="38" spans="3:7" x14ac:dyDescent="0.3">
@@ -2095,38 +2152,33 @@
     </row>
     <row r="46" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C46" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="D46" s="20" t="str">
+        <v>124</v>
+      </c>
+      <c r="D46" s="27" t="str">
         <f>"( " &amp; D11 &amp; " )"</f>
         <v>( Rizky )</v>
       </c>
-      <c r="E46" s="20"/>
-      <c r="F46" s="20"/>
+      <c r="E46" s="27"/>
+      <c r="F46" s="27"/>
       <c r="G46" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="47" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C47" s="14" t="s">
-        <v>126</v>
-      </c>
-      <c r="D47" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="E47" s="21"/>
-      <c r="F47" s="21"/>
+        <v>125</v>
+      </c>
+      <c r="D47" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="E47" s="28"/>
+      <c r="F47" s="28"/>
       <c r="G47" s="14" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B3:H3"/>
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="B6:H6"/>
-    <mergeCell ref="G16:H16"/>
     <mergeCell ref="D46:F46"/>
     <mergeCell ref="D47:F47"/>
     <mergeCell ref="G17:H17"/>
@@ -2140,19 +2192,30 @@
     <mergeCell ref="B27:H27"/>
     <mergeCell ref="B28:H28"/>
     <mergeCell ref="G23:H23"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="B6:H6"/>
+    <mergeCell ref="G16:H16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="80" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="72" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F4C1D341-E16A-4230-8353-8C60404EE3E0}">
           <x14:formula1>
             <xm:f>Database!$C$4:$C$15</xm:f>
           </x14:formula1>
           <xm:sqref>D8</xm:sqref>
         </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{1E1314EA-DA43-483C-9190-8666753CB2C9}">
+          <x14:formula1>
+            <xm:f>Database!$C$18:$C$25</xm:f>
+          </x14:formula1>
+          <xm:sqref>C17:C23</xm:sqref>
+        </x14:dataValidation>
       </x14:dataValidations>
     </ext>
   </extLst>
